--- a/tables/NULL_ALLELES.xlsx
+++ b/tables/NULL_ALLELES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\Bison_github\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672A429F-E059-48EA-8F08-796C6C78B828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FF4662-1BEB-4575-B635-167ED9B01823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="53">
   <si>
     <t>Population</t>
   </si>
@@ -186,6 +186,42 @@
       </rPr>
       <t>T2</t>
     </r>
+  </si>
+  <si>
+    <t>WENT</t>
+  </si>
+  <si>
+    <t>BM1225</t>
+  </si>
+  <si>
+    <t>BM1862</t>
+  </si>
+  <si>
+    <t>NORD</t>
+  </si>
+  <si>
+    <t>BM4440</t>
+  </si>
+  <si>
+    <t>NAH</t>
+  </si>
+  <si>
+    <t>BM720</t>
+  </si>
+  <si>
+    <t>BMS1315</t>
+  </si>
+  <si>
+    <t>IL4</t>
+  </si>
+  <si>
+    <t>SPS115</t>
+  </si>
+  <si>
+    <t>TGLA122</t>
+  </si>
+  <si>
+    <t>TGLA53</t>
   </si>
 </sst>
 </file>
@@ -259,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -285,6 +321,46 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,17 +642,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" style="1" customWidth="1"/>
     <col min="4" max="5" width="12.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="13.42578125" style="13" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="12"/>
+    <col min="9" max="9" width="12" style="12" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -589,8 +669,20 @@
       <c r="D1" s="8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -603,8 +695,20 @@
       <c r="D2" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="19">
+        <v>0.10566</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
@@ -617,8 +721,20 @@
       <c r="D3" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F3" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="19">
+        <v>0.16298000000000001</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
@@ -631,8 +747,20 @@
       <c r="D4" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F4" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="20">
+        <v>0.15257000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>33</v>
       </c>
@@ -645,8 +773,20 @@
       <c r="D5" s="6">
         <v>0.11025</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="19">
+        <v>0.11065</v>
+      </c>
+      <c r="I5" s="19">
+        <v>0.10356</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -659,8 +799,20 @@
       <c r="D6" s="3">
         <v>0.14581</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0.11025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
@@ -673,8 +825,20 @@
       <c r="D7" s="6">
         <v>0.11509999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F7" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="20">
+        <v>0.16177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
@@ -687,8 +851,20 @@
       <c r="D8" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0.14581</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
@@ -701,8 +877,20 @@
       <c r="D9" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0.1207</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -715,8 +903,20 @@
       <c r="D10" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F10" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="20">
+        <v>0.11509999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -729,8 +929,20 @@
       <c r="D11" s="6">
         <v>0.16492999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" s="19">
+        <v>0.11097</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -743,8 +955,20 @@
       <c r="D12" s="3">
         <v>0.11595999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F12" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="19">
+        <v>0.15257000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>2</v>
       </c>
@@ -757,8 +981,20 @@
       <c r="D13" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F13" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="20">
+        <v>0.20821999999999999</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
@@ -771,8 +1007,20 @@
       <c r="D14" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="19">
+        <v>0.16408</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
@@ -785,8 +1033,20 @@
       <c r="D15" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0.11065</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>29</v>
       </c>
@@ -799,8 +1059,20 @@
       <c r="D16" s="3">
         <v>0.10989</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F16" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="20">
+        <v>0.14584</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
@@ -813,8 +1085,20 @@
       <c r="D17" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F17" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="19">
+        <v>0.13200999999999999</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>6</v>
       </c>
@@ -827,8 +1111,20 @@
       <c r="D18" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F18" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="20">
+        <v>0.16492999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
@@ -841,8 +1137,20 @@
       <c r="D19" s="6">
         <v>0.11249000000000001</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F19" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="20">
+        <v>0.26895000000000002</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
@@ -855,8 +1163,20 @@
       <c r="D20" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F20" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" s="19">
+        <v>0.10813</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -869,8 +1189,20 @@
       <c r="D21" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F21" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="19">
+        <v>0.11595999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
@@ -883,8 +1215,20 @@
       <c r="D22" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" s="19">
+        <v>0.19830999999999999</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>28</v>
       </c>
@@ -897,8 +1241,20 @@
       <c r="D23" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F23" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="20">
+        <v>0.23618</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>6</v>
       </c>
@@ -911,8 +1267,20 @@
       <c r="D24" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F24" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="19">
+        <v>0.18776999999999999</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>11</v>
       </c>
@@ -925,8 +1293,20 @@
       <c r="D25" s="3">
         <v>0.10346</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" s="19">
+        <v>0.15257000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>14</v>
       </c>
@@ -939,8 +1319,21 @@
       <c r="D26" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F26" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="19">
+        <v>0.11006000000000001</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="K26" s="22"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -953,8 +1346,20 @@
       <c r="D27" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F27" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0.16486999999999999</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>20</v>
       </c>
@@ -967,8 +1372,20 @@
       <c r="D28" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F28" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="20">
+        <v>0.11065</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>29</v>
       </c>
@@ -981,8 +1398,20 @@
       <c r="D29" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F29" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I29" s="20">
+        <v>0.10989</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
@@ -995,8 +1424,20 @@
       <c r="D30" s="3">
         <v>0.19170000000000001</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F30" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I30" s="20">
+        <v>0.15257000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
@@ -1009,8 +1450,20 @@
       <c r="D31" s="6">
         <v>0.13009999999999999</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F31" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I31" s="19">
+        <v>0.16177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>6</v>
       </c>
@@ -1023,8 +1476,20 @@
       <c r="D32" s="3">
         <v>0.10058</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F32" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="19">
+        <v>0.10478999999999999</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>30</v>
       </c>
@@ -1037,8 +1502,20 @@
       <c r="D33" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F33" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I33" s="19">
+        <v>0.10732999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>4</v>
       </c>
@@ -1051,8 +1528,20 @@
       <c r="D34" s="3">
         <v>0.10757</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F34" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="20">
+        <v>0.12543000000000001</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>6</v>
       </c>
@@ -1065,8 +1554,20 @@
       <c r="D35" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I35" s="19">
+        <v>0.11249000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>2</v>
       </c>
@@ -1078,6 +1579,480 @@
       </c>
       <c r="D36" s="11">
         <v>0.14254</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I36" s="19">
+        <v>0.11773</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F37" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="20">
+        <v>0.15742999999999999</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F38" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="20">
+        <v>0.12271</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F39" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="20">
+        <v>0.29028999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F40" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I40" s="19">
+        <v>0.14507999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F41" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="19">
+        <v>0.11752</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="19">
+        <v>0.11027000000000001</v>
+      </c>
+      <c r="I42" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F43" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="20">
+        <v>0.12528</v>
+      </c>
+      <c r="I43" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F44" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I44" s="20">
+        <v>0.10346</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F45" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="20">
+        <v>0.11989</v>
+      </c>
+      <c r="I45" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F46" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I46" s="20">
+        <v>0.126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F47" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="20">
+        <v>0.13086</v>
+      </c>
+      <c r="I47" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F48" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I48" s="20">
+        <v>0.19664999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F49" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H49" s="19">
+        <v>0.19170000000000001</v>
+      </c>
+      <c r="I49" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F50" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H50" s="19">
+        <v>0.11928</v>
+      </c>
+      <c r="I50" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F51" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I51" s="19">
+        <v>0.19664999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F52" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I52" s="20">
+        <v>0.19170000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F53" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I53" s="20">
+        <v>0.10599</v>
+      </c>
+    </row>
+    <row r="54" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F54" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I54" s="20">
+        <v>0.19664999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F55" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H55" s="19">
+        <v>0.23618</v>
+      </c>
+      <c r="I55" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F56" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I56" s="20">
+        <v>0.13009999999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F57" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" s="20">
+        <v>0.11323</v>
+      </c>
+    </row>
+    <row r="58" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F58" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I58" s="19">
+        <v>0.10058</v>
+      </c>
+    </row>
+    <row r="59" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F59" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I59" s="19">
+        <v>0.11413</v>
+      </c>
+    </row>
+    <row r="60" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F60" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G60" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I60" s="20">
+        <v>0.23296</v>
+      </c>
+    </row>
+    <row r="61" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F61" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I61" s="20">
+        <v>0.17352999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F62" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H62" s="20">
+        <v>0.15651999999999999</v>
+      </c>
+      <c r="I62" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F63" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H63" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I63" s="19">
+        <v>0.10757</v>
+      </c>
+    </row>
+    <row r="64" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F64" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H64" s="19">
+        <v>0.13886000000000001</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="65" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F65" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H65" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I65" s="19">
+        <v>0.15257000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F66" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="20">
+        <v>0.12037</v>
+      </c>
+      <c r="I66" s="20">
+        <v>0.14254</v>
+      </c>
+    </row>
+    <row r="67" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F67" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H67" s="19">
+        <v>0.19830999999999999</v>
+      </c>
+      <c r="I67" s="19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F68" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G68" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H68" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="I68" s="20">
+        <v>0.24709</v>
+      </c>
+    </row>
+    <row r="69" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F69" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G69" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H69" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="I69" s="25">
+        <v>0.16408</v>
       </c>
     </row>
   </sheetData>
